--- a/daily_matches/job_matches_2026-07-31.xlsx
+++ b/daily_matches/job_matches_2026-07-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Cloud Engineer - AWS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Great American Insurance Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Keras, S3</t>
+          <t>RAG, AWS SageMaker, S3, Glue, Athena, Kinesis, Docker, Kubernetes, AKS, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a69ee2362e8f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=5bf61388569c1188</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Analyst (Hybrid - Madison or Austin)</t>
+          <t>Software Engineer III - Databricks</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Redshift, Tableau</t>
+          <t>RAG, TensorFlow, EC2, Kubernetes, CI/CD, Terraform, Databricks, PySpark, Kafka, Cassandra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=289d005fb52fdb68</t>
+          <t>https://www.indeed.com/viewjob?jk=e3097ac152749d4d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data</t>
+          <t>AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dutch Bros Coffee</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, Docker, Kubernetes, CI/CD, Snowflake, Databricks, PySpark, Kafka</t>
+          <t>AI Engineer, LangChain, RAG, Pinecone, S3, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=033eef2f59a1ddd9</t>
+          <t>https://www.indeed.com/viewjob?jk=c716bd22ae576c5e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III - C# / Java</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Novanta</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, Terraform, Git, MongoDB, Cassandra, NoSQL, Python, SQL</t>
+          <t>RAG, Redshift, BigQuery, CI/CD, GitHub Actions, Git, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=735136a340f06328</t>
+          <t>https://www.indeed.com/viewjob?jk=1d84674d8dbd92bd</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI, AWS DevOps, Java/Python Software Engineer III</t>
+          <t>Applied AI Engineer III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,137 +636,137 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65068caf46548141</t>
+          <t>https://www.indeed.com/viewjob?jk=c84476dc78d41318</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>R&amp;D Management Trainee - Full-Stack Engineer (Backend)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, MySQL, NoSQL, SQL</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, CI/CD, Git, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec9b8320959ff15</t>
+          <t>https://www.indeed.com/viewjob?jk=8f2d281e2915619c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist/ AI Engineer</t>
+          <t>R&amp;D Management Trainee - Full-Stack Engineer (Backend)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, TensorFlow, PyTorch, Data Lake, Git</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, CI/CD, Git, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6966a1bb01bb09af</t>
+          <t>https://www.indeed.com/viewjob?jk=98bc18d2d0c8b52b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>R&amp;D Management Trainee - Full-Stack Engineer (Backend)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>U.S. Pharmacopeia</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Hugging Face, Pinecone, Prompt Engineering, Docker, Git</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, CI/CD, Git, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ceded799842766</t>
+          <t>https://www.indeed.com/viewjob?jk=2102fddda3230c3c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Java Full stack Developer (NoSQl and Solr exp)</t>
+          <t>R&amp;D Management Trainee - Full-Stack Engineer (Backend)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Kafka, MongoDB, Cassandra, NoSQL, SQL, R, Java</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, CI/CD, Git, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,54 +776,54 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac257c5a1deaaa8</t>
+          <t>https://www.indeed.com/viewjob?jk=e3c144394ede40c4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Security Automation Engineer</t>
+          <t>R&amp;D Management Trainee - Full-Stack Engineer (Backend)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Symbotic</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, BigQuery, Docker, CI/CD, BigQuery, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, CI/CD, Git, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=735c933dd69186e6</t>
+          <t>https://www.indeed.com/viewjob?jk=25a4b2100524729d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -832,11 +832,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LLaMA, Gemini, Copilot, Prompt Engineering, Git, MySQL, Python, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, AWS SageMaker, MLflow, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780f9e209d274d6d</t>
+          <t>https://www.indeed.com/viewjob?jk=19c1fe701c89ab64</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Applied AI SRE III - PxE GPS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RLDatix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, MySQL, Python, SQL, R</t>
+          <t>RAG, MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96149f05f775cf47</t>
+          <t>https://www.indeed.com/viewjob?jk=d84df72ea9532c51</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Applied AI SRE III - PxE GPS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Itech Edge</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5791b55d6da1365</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c8966b4d59c6b1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Applied AI SRE III - PxE GPS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, MLflow, Docker, Kubernetes, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa9c3eab7480e319</t>
+          <t>https://www.indeed.com/viewjob?jk=62830a371d1e64c4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI/ML</t>
+          <t>Applied AI SRE III - PxE GPS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3031aa7626b2c82</t>
+          <t>https://www.indeed.com/viewjob?jk=7b49a235e6405f16</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI/ML</t>
+          <t>Applied AI SRE III - PxE GPS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5320a3d327d2100</t>
+          <t>https://www.indeed.com/viewjob?jk=1135d93688985c7c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI/ML</t>
+          <t>Software Development Engineer Intern</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Republic Finance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b20ccd3b810382</t>
+          <t>https://www.indeed.com/viewjob?jk=7d3cc0bd365d4d42</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI/ML</t>
+          <t>Senior Software Engineer, Ecommerce Web Applications (US/Canada)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CSC Generation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=834d216112729c57</t>
+          <t>https://www.indeed.com/viewjob?jk=a55d577c0fda86f2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI/ML</t>
+          <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Lyra Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, FastAPI, Docker, Kubernetes, Python, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e31fd99ea2f29527</t>
+          <t>https://www.indeed.com/viewjob?jk=581cdb2bb53ae377</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AI/ML Backend Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>Lyra Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, FastAPI, Docker, Kubernetes, Python, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2d7da2fb1097af</t>
+          <t>https://www.indeed.com/viewjob?jk=de02008f413aa78a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Scientist/ AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, TensorFlow, PyTorch, Data Lake, Git</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=681bd8a4ac4bc742</t>
+          <t>https://www.indeed.com/viewjob?jk=4e7f74e0aac56c7e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, FastAPI, Terraform, Git, Python, R, Scala</t>
+          <t>Docker, CI/CD, Git, PostgreSQL, MongoDB, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1205a6612a0a81b1</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd3a77f9dc14549</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - Live Operations</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, MLflow, Kafka, Python, R, Java, Scala</t>
+          <t>Copilot, Docker, CI/CD, Git, Snowflake, Databricks, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77af677ef7a92a67</t>
+          <t>https://www.indeed.com/viewjob?jk=87b420bcd07d16a3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Specialist - Software Engineering</t>
+          <t>Junior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, MongoDB, SQL, R, Java</t>
+          <t>Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f7a16c8d563ec1a</t>
+          <t>https://www.indeed.com/viewjob?jk=22e5eb1f68ce4fa1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer I IS - Remote</t>
+          <t>AI Agentic Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Kuehne+Nagel</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897bf28e61272194</t>
+          <t>https://www.indeed.com/viewjob?jk=d5289274fa574849</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer I IS - Remote</t>
+          <t>Senior DevOps Engineer II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Kinesis, CI/CD, GitHub Actions, Terraform, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58ba9261e816b30d</t>
+          <t>https://www.indeed.com/viewjob?jk=a4dd6d4d1250416d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer I IS - Remote</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac45d2336f958fc</t>
+          <t>https://www.indeed.com/viewjob?jk=f2757c88489fb070</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer I IS - Remote</t>
+          <t>Application Software Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McGregor, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=181a80ce2b67f3fc</t>
+          <t>https://www.indeed.com/viewjob?jk=7b76bf631e49eaf7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer I IS - Remote</t>
+          <t>Application Software Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aecce9c7139e7c8</t>
+          <t>https://www.indeed.com/viewjob?jk=d840263db58e7c35</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer I IS - Remote</t>
+          <t>Application Software Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lubbock, TX, US USA</t>
+          <t>Hawthorne, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e56f23aa07f0964</t>
+          <t>https://www.indeed.com/viewjob?jk=7fb5100f75bd78f4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer I IS - Remote</t>
+          <t>Application Software Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Napa, CA, US USA</t>
+          <t>Bastrop, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fec3be32abfcec5</t>
+          <t>https://www.indeed.com/viewjob?jk=9e73a88ee290a958</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Application Software Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vanta</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cape Canaveral, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b59d72dc36b6ebb</t>
+          <t>https://www.indeed.com/viewjob?jk=476d48b6e8093f27</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Quality Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>National Interstate</t>
+          <t>New American Funding</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Richfield, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, SQL, R</t>
+          <t>Data Scientist, RAG, Cortex, CI/CD, Git, Snowflake, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc40fae37ed3a1b</t>
+          <t>https://www.indeed.com/viewjob?jk=e1fdb354a3224518</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python/Databricks/AI</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Great American Insurance Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Databricks, Kafka, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Pinecone, Prompt Engineering, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934b0464c016b33e</t>
+          <t>https://www.indeed.com/viewjob?jk=512023994ebecf60</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CMAS-Software Engineer III</t>
+          <t>Senior Engineer - Artificial Intelligence</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, Terraform, Git, PostgreSQL, MongoDB, Python, SQL, R, Scala</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,42 +1686,812 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=438fc9e3b0ce701a</t>
+          <t>https://www.indeed.com/viewjob?jk=02e50929b798d2e5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Analytics and Research Analyst</t>
+          <t>Senior Engineer - Artificial Intelligence</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df0d96b7d77dc313</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Generative AI Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>INFINITE ELECTRONICS</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, FastAPI, Docker, CI/CD, PySpark, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fddfd8b8743b9b5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>IT Systems Engineer III</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Delan Associates, Inc</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Palm Beach Gardens, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, CI/CD, GitHub Actions, Git, PostgreSQL, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=371bf76528aae202</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Business Intelligence (BI) Developer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Scope Infotech</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Columbia, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Data Scientist, Redshift, Synapse, Snowflake, Redshift, Tableau, Power BI, Quicksight, SQL, R</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02f9240f8b5c9344</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Network Software Test Engineer IV</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Hewlett Packard Enterprise | HPE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Roseville, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a74f967b68ce859</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Software Engineering SMTS</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d30ffa678824b6d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Software Engineer - Sr. Consultant level</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Copilot, MySQL, MongoDB, Cassandra, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82bcde7b54f0934f</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Jr Data Scientist</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Focus Camera</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Brooklyn, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Data Scientist, Git, MySQL, Power BI, Python, SQL, R, Scala, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0686708bc75a8527</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Gemini, FastAPI, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3c438d663f378f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Systems Engineer, Product Platform Tools</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Cloudflare</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ab7c5beaf9c085b</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>The Providence Groups</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>White House, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Synapse, Git, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a74f52ad1347dc4</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Research Engineer - Energy Markets</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Greenwood Village, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58c7a6a1cd090d27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>AI Engineer- NLP</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Velocitor Solutions</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, FastAPI, Terraform, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87d03162b92a10d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Architect</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>EchoStar</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>Herndon, VA, US USA</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D50" t="n">
         <v>10</v>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a219d393491c41eb</t>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, Git, Databricks, Kafka, Hadoop, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d05eb1236a241ecf</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Neighbor</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Lehi, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Athena, Redshift, Data Lake, CI/CD, Redshift, SQL, R</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05abf83ff575c074</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Lyra Health</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, FastAPI, Docker, Kubernetes, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f254f2bf1c7c5a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Sr Machine Learning Engineer, Adobe Firefly Services</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, PyTorch, Kubernetes, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14d5cf66d703b708</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Delivery Senior Consultant, Data Engineering and Gen AI Conversion Solutions</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, Keras, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2657940cb808f640</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Delivery Senior Consultant, Data Engineering and Gen AI Conversion Solutions</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, Keras, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=300ea67fd4b912aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Delivery Senior Consultant, Data Engineering and Gen AI Conversion Solutions</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, Keras, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f77cd65595d2ef6</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Machine Learning Intelligent Operations Team - Quant Analytics Senior Associate</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, XGBoost, LightGBM, Git, Snowflake, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20556270e92e56e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>CI/CD, Jenkins, Git, MySQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08083d178d541b5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior Core Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Terraform, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3947ba5895fba97</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-31.xlsx
+++ b/daily_matches/job_matches_2026-07-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,542 +486,157 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Glue, FastAPI, CI/CD, Terraform, Git, PySpark, Kafka</t>
+          <t>LangChain, RAG, LLaMA, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba8335e79adaef9</t>
+          <t>https://www.indeed.com/viewjob?jk=46bd797613407be6</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Coforge</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, Gemini, Prompt Engineering, S3, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a5597d7720fb2e0</t>
+          <t>https://www.indeed.com/viewjob?jk=05510e6f1caeddd8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Senior Associate- Full Stack Software Engineer- AI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>State Air Resources Board</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, EC2, Glue, Docker, CI/CD, Terraform, Git, PostgreSQL</t>
+          <t>Data Scientist, LangChain, RAG, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f8755d5755bfc0f</t>
+          <t>https://www.indeed.com/viewjob?jk=4b40647e800c14f2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>Senior Data Analytics and Research Analyst</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Funko</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Burbank, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Prompt Engineering, CI/CD, Git, Snowflake</t>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4548f2eb58087af</t>
+          <t>https://www.indeed.com/viewjob?jk=a3674dda2f0400bd</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>Data Analytics and Research Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Funko</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Everett, WA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Prompt Engineering, CI/CD, Git, Snowflake</t>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d27168c9b9262d4</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Virta Health</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, BigQuery, Kubernetes, CI/CD, GitHub Actions, Git, BigQuery, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=671761ff02fb6ab9</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Java Backend Software Engineer III - Cassandra / Kubernetes</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, Cassandra, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=332e34fec720158e</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AI ML Engineer - Python | Berkeley Heights, NJ or SFO, CA ( 5days onsite) - F2F interview required</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Next Gen Software Solutions</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Berkeley Heights, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, Docker, CI/CD, Jenkins, Snowflake, MySQL, MongoDB, NoSQL, Python</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cdde7e57b19e49e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior UX Software Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>GRVTY</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>S3, EC2, Docker, Git, MySQL, MongoDB, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=188385fe594d1176</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, Git, Hadoop, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eadf996ee09b3cc6</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Quality Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, MySQL, MongoDB, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=82aa255d3d6e23a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Full Stack (Java &amp; Kafka) (Cloud Operations Resilience Engineering)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=851b1e9451e42a90</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Full Stack (Java &amp; Kafka) (Cloud Operations Resilience Engineering)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Riverwoods, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8be459cc3686f5d</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Data Engineer II - Zelle</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Early Warning Services</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Scottsdale, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, S3, Git, Hadoop, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=18ad7ae6038eba44</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist - AI and ECG</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>The University of Michigan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ann Arbor, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bccf3d9de1d65d82</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Applied AI Scholar in Residence</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Waukesha County Technical College</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Pewaukee, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a2b76de2dee8c1e</t>
+          <t>https://www.indeed.com/viewjob?jk=d98789fa82948dbd</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-31.xlsx
+++ b/daily_matches/job_matches_2026-07-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>senior data engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL</t>
+          <t>Data Scientist, Generative AI, Redshift, BigQuery, Synapse, Data Lake, Kubernetes, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46bd797613407be6</t>
+          <t>https://www.indeed.com/viewjob?jk=6348f1b22dfd1649</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>Stylitics</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
+          <t>RAG, BigQuery, Docker, Kubernetes, CI/CD, Terraform, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05510e6f1caeddd8</t>
+          <t>https://www.indeed.com/viewjob?jk=d143b966366bb7dc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Associate- Full Stack Software Engineer- AI</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Inabia Software &amp; Consulting Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Grand Prairie, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Terraform, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Snowflake, Databricks, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b40647e800c14f2</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5a293e9054cf01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Analytics and Research Analyst</t>
+          <t>Senior Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Woodinville, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Azure ML, Redshift, CI/CD, Snowflake, Databricks, Redshift, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,42 +601,147 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3674dda2f0400bd</t>
+          <t>https://www.indeed.com/viewjob?jk=2720ca648b440e85</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Analytics and Research Analyst</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>Galls</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Gemini, Git, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef285ddfac0bbe09</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Galls</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Lexington, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Gemini, Git, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=241cc5e63f410a63</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Software Engineer - Full-Stack</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Reliant Health Partners</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>10</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Terraform, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d98789fa82948dbd</t>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47634b1c6a87e396</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Utility AI Interaction Designer - Co-Op II</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>City of Charlotte, NC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, Copilot, Prompt Engineering, Git, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04aeea58cd24eccf</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-31.xlsx
+++ b/daily_matches/job_matches_2026-07-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>senior data engineer</t>
+          <t>Cloud Data Platform Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Northern Trust Corp.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>26.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Redshift, BigQuery, Synapse, Data Lake, Kubernetes, CI/CD, Git, Snowflake</t>
+          <t>Data Scientist, RAG, Copilot, S3, Glue, Athena, Redshift, Synapse, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6348f1b22dfd1649</t>
+          <t>https://www.indeed.com/viewjob?jk=c3babca04d3a4353</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Databricks Senior Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Stylitics</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Docker, Kubernetes, CI/CD, Terraform, BigQuery, Python, SQL, R</t>
+          <t>RAG, Redshift, BigQuery, Synapse, CI/CD, Terraform, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d143b966366bb7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=14e6d9e0e8ac190f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>MLOps / LLMOps Engineer (GenAI Platform)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Inabia Software &amp; Consulting Inc.</t>
+          <t>Unitedone health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Grand Prairie, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Snowflake, Databricks, Kafka, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, LLaMA, Mistral, Hugging Face, Azure ML, MLflow, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5a293e9054cf01</t>
+          <t>https://www.indeed.com/viewjob?jk=ebb4f0e5c1dd6fef</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Architect</t>
+          <t>Senior Associate, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Redapt inc</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Woodinville, WA, US USA</t>
+          <t>Westborough, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Azure ML, Redshift, CI/CD, Snowflake, Databricks, Redshift, Python, SQL</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, Docker, AKS, CI/CD, Git, Snowflake, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,19 +601,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2720ca648b440e85</t>
+          <t>https://www.indeed.com/viewjob?jk=48cb6757f61255ed</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Galls</t>
+          <t>Planned Systems International</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,81 +622,81 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Gemini, Git, Tableau, Power BI, Python, SQL, R, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef285ddfac0bbe09</t>
+          <t>https://www.indeed.com/viewjob?jk=9b5f0db6b1f03476</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Galls</t>
+          <t>Planned Systems International</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lexington, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Gemini, Git, Tableau, Power BI, Python, SQL, R, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=241cc5e63f410a63</t>
+          <t>https://www.indeed.com/viewjob?jk=1d9425f229266472</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer - Full-Stack</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Reliant Health Partners</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Terraform, Git, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, Git, Snowflake, Kafka, MongoDB, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,42 +706,567 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47634b1c6a87e396</t>
+          <t>https://www.indeed.com/viewjob?jk=74263f4a52c96ca9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Utility AI Interaction Designer - Co-Op II</t>
+          <t>Senior Specialist - Architecture</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>City of Charlotte, NC</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Kafka</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43f485e0d1a3ced7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AI Architect/AI Subject Matter Expert</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Techtorch</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Prompt Engineering, FastAPI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0d5a8b5decdbb3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AI &amp; Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Schneider</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Green Bay, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, Docker, Kubernetes, CI/CD, Git, Kafka, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb8ed30d83b4e5e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SumUp</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Boulder, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=433f1d92386f45a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Investment Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Arrowstreet Capital LP</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=563a190ef6b3a0b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Computer Vision Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Meridian Infotech Limited</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Asheville, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, OpenCV, MLflow, FastAPI, Docker, Kubernetes, CI/CD, Python, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9aef2707ec9273e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Automation Engineer / SDET (AI Tooling &amp; Test Automation)- Hybrid-Atlanta</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Power BI, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5eb548bbff8792dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Infrastructure Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Cloud Destinations</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6918c52bf63c739a</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Software Engineer II – Java, Spring Boot &amp; React</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Entrust Corporation</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Shakopee, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Jenkins, Git, PostgreSQL, MySQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9bef5ac6ac4e1578</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Test (Org Modeling)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ServiceTitan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f3310018661e14c</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Machine Intelligence Analyst- P&amp;HVAC</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sunbelt Rentals</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Fort Mill, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f029eeca827e77d</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Havis Inc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Plymouth, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8041a8f40b8b4cc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Havis Inc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Burnsville, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ae0b8e36a12d558</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Havis Inc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Warminster, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9736057b1f28dece</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Havis Inc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Hilliard, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c94c02ff7c966f4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Security Engineer- Application Security &amp; Cloud</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dot Foods, Inc.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Chesterfield, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>10</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Generative AI, Gemini, Copilot, Prompt Engineering, Git, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04aeea58cd24eccf</t>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=749cd1955b2de945</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-31.xlsx
+++ b/daily_matches/job_matches_2026-07-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer</t>
+          <t>Databricks Platform &amp; Database Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Northern Trust Corp.</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.7</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, S3, Glue, Athena, Redshift, Synapse, Docker, Kubernetes</t>
+          <t>Data Scientist, Prompt Engineering, TensorFlow, PyTorch, S3, MLflow, CI/CD, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3babca04d3a4353</t>
+          <t>https://www.indeed.com/viewjob?jk=28b754997a6cb19c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Databricks Senior Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Synapse, CI/CD, Terraform, Snowflake, Databricks, BigQuery, Redshift</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Data Lake, FastAPI, Kubernetes, AKS, CI/CD, Terraform, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e6d9e0e8ac190f</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d4d6b724af8274</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MLOps / LLMOps Engineer (GenAI Platform)</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unitedone health</t>
+          <t>Mitratech</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, LLaMA, Mistral, Hugging Face, Azure ML, MLflow, Docker</t>
+          <t>AI Engineer, LangChain, RAG, FastAPI, Docker, CI/CD, GitHub Actions, Git, Snowflake, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebb4f0e5c1dd6fef</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fad79af5600169</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Associate, Full-Stack Engineer</t>
+          <t>Solutions Architect (GenAI, Python/Data, AWS)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Westborough, MA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, Docker, AKS, CI/CD, Git, Snowflake, Kafka</t>
+          <t>RAG, Copilot, S3, FastAPI, Docker, Kubernetes, Apache Airflow, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,102 +601,102 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48cb6757f61255ed</t>
+          <t>https://www.indeed.com/viewjob?jk=84992a9d853e715d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Solutions Architect (GenAI, Python/Data, AWS)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Planned Systems International</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes</t>
+          <t>RAG, Copilot, S3, FastAPI, Docker, Kubernetes, Apache Airflow, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b5f0db6b1f03476</t>
+          <t>https://www.indeed.com/viewjob?jk=794fcf67de18d24f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Planned Systems International</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes</t>
+          <t>RAG, Azure ML, Synapse, Data Lake, MLflow, CI/CD, Databricks, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d9425f229266472</t>
+          <t>https://www.indeed.com/viewjob?jk=3d37b8249fccee88</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, Git, Snowflake, Kafka, MongoDB, SQL</t>
+          <t>Data Scientist, Generative AI, Copilot, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74263f4a52c96ca9</t>
+          <t>https://www.indeed.com/viewjob?jk=f837fff6b7bebf22</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Specialist - Architecture</t>
+          <t>Sustainability Data and AI Consultant</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Kafka</t>
+          <t>Gemini, TensorFlow, PyTorch, Data Lake, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f485e0d1a3ced7</t>
+          <t>https://www.indeed.com/viewjob?jk=53fb69889e7f589a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Architect/AI Subject Matter Expert</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Techtorch</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Prompt Engineering, FastAPI, CI/CD, Git</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0d5a8b5decdbb3e</t>
+          <t>https://www.indeed.com/viewjob?jk=edefefd43be9dc66</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>Compass Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, MLflow, Docker, Kubernetes, CI/CD, Git, Kafka, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8ed30d83b4e5e2</t>
+          <t>https://www.indeed.com/viewjob?jk=fbf25f49dcaa3bab</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SumUp</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Madison, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=433f1d92386f45a1</t>
+          <t>https://www.indeed.com/viewjob?jk=be3d62c77468bade</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Investment Analytics Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Arrowstreet Capital LP</t>
+          <t>Compass Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563a190ef6b3a0b1</t>
+          <t>https://www.indeed.com/viewjob?jk=f225032bbf5d84c7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Computer Vision Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Meridian Infotech Limited</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Asheville, NC, US USA</t>
+          <t>Aventura, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, OpenCV, MLflow, FastAPI, Docker, Kubernetes, CI/CD, Python, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aef2707ec9273e1</t>
+          <t>https://www.indeed.com/viewjob?jk=a1b07860a5889799</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Automation Engineer / SDET (AI Tooling &amp; Test Automation)- Hybrid-Atlanta</t>
+          <t>Agentic Software Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>arrivia</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Power BI, Python, R, Java</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, Docker, CI/CD, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb548bbff8792dd</t>
+          <t>https://www.indeed.com/viewjob?jk=88140868e5fe967c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Infrastructure Automation Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cloud Destinations</t>
+          <t>Modus Closing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6918c52bf63c739a</t>
+          <t>https://www.indeed.com/viewjob?jk=f3134c6730945c7c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer II – Java, Spring Boot &amp; React</t>
+          <t>Sr Engineer - Stores &amp; Supply Chain</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Entrust Corporation</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Shakopee, MN, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Jenkins, Git, PostgreSQL, MySQL, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Docker, CI/CD, Kafka, MongoDB, Cassandra, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bef5ac6ac4e1578</t>
+          <t>https://www.indeed.com/viewjob?jk=00968f936d1004ed</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Test (Org Modeling)</t>
+          <t>Sr. Data Modeler 4D</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Databricks, PySpark, Hadoop, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f3310018661e14c</t>
+          <t>https://www.indeed.com/viewjob?jk=58941ecd857176c7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Machine Intelligence Analyst- P&amp;HVAC</t>
+          <t>Quantum Software Engineer - Nuclear</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>Infleqtion</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, SQL, R, Optimization</t>
+          <t>RAG, FastAPI, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Julia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f029eeca827e77d</t>
+          <t>https://www.indeed.com/viewjob?jk=bfcb1894126dab65</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer II - Fleet Enablement &amp; Insights</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Havis Inc</t>
+          <t>TORC Robotics</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plymouth, MI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, S3, Git, Databricks, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8041a8f40b8b4cc1</t>
+          <t>https://www.indeed.com/viewjob?jk=37856ba8342c5bdf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Agent Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Havis Inc</t>
+          <t>Delta Faucet Company</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Burnsville, MN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>LangChain, RAG, Copilot, MLflow, Databricks, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae0b8e36a12d558</t>
+          <t>https://www.indeed.com/viewjob?jk=379366fceb0a12ba</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Solutions Engineer - Columbus, Ohio - NOT ACCEPTING AGENCY CANDIDATES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Havis Inc</t>
+          <t>Wasserstrom</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Warminster, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Copilot, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9736057b1f28dece</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0b5bd1d4503d38</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Platform Operations Engineer, Infrastucture</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Havis Inc</t>
+          <t>Viome Life Sciences</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hilliard, OH, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Kubernetes, AKS, Terraform, PostgreSQL, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,42 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94c02ff7c966f4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Security Engineer- Application Security &amp; Cloud</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Dot Foods, Inc.</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Chesterfield, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=749cd1955b2de945</t>
+          <t>https://www.indeed.com/viewjob?jk=b687743491edb71c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-31.xlsx
+++ b/daily_matches/job_matches_2026-07-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Databricks Platform &amp; Database Engineer</t>
+          <t>Engineer 2 - Integrated Merchandising</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>14.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Prompt Engineering, TensorFlow, PyTorch, S3, MLflow, CI/CD, Terraform, Git, Snowflake</t>
+          <t>BigQuery, Kubernetes, CI/CD, Terraform, BigQuery, Kafka, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b754997a6cb19c</t>
+          <t>https://www.indeed.com/viewjob?jk=14c1f123eec910b1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Experienced AI Engineer - Generative AI/Machine Learning</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>RLI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Data Lake, FastAPI, Kubernetes, AKS, CI/CD, Terraform, Databricks</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d4d6b724af8274</t>
+          <t>https://www.indeed.com/viewjob?jk=a38a95da17436915</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Engineer 2: AI Agentic Solutions (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mitratech</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, FastAPI, Docker, CI/CD, GitHub Actions, Git, Snowflake, MongoDB</t>
+          <t>RAG, Prompt Engineering, Redshift, BigQuery, Docker, Kubernetes, CI/CD, BigQuery, Redshift, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fad79af5600169</t>
+          <t>https://www.indeed.com/viewjob?jk=33925c5bce70e9c4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Solutions Architect (GenAI, Python/Data, AWS)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>Jazwares</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, FastAPI, Docker, Kubernetes, Apache Airflow, CI/CD, GitHub Actions, Git</t>
+          <t>RAG, Glue, Redshift, CI/CD, Git, Snowflake, Databricks, Redshift, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84992a9d853e715d</t>
+          <t>https://www.indeed.com/viewjob?jk=0bec398ccd65219f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Solutions Architect (GenAI, Python/Data, AWS)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>NCR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, FastAPI, Docker, Kubernetes, Apache Airflow, CI/CD, GitHub Actions, Git</t>
+          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794fcf67de18d24f</t>
+          <t>https://www.indeed.com/viewjob?jk=882b597f41774c2d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps/Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>Volt Lighting</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Lutz, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Azure ML, Synapse, Data Lake, MLflow, CI/CD, Databricks, Tableau, Power BI, Python</t>
+          <t>AI Engineer, RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d37b8249fccee88</t>
+          <t>https://www.indeed.com/viewjob?jk=1be18f7733f3d252</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Copilot, TensorFlow, PyTorch, Git, Hadoop, Tableau, Power BI, Python</t>
+          <t>Generative AI, RAG, Gemini, Copilot, Git, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f837fff6b7bebf22</t>
+          <t>https://www.indeed.com/viewjob?jk=1c71808bd9c68661</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sustainability Data and AI Consultant</t>
+          <t>Data Scientist Cloud - SME</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Odenton, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gemini, TensorFlow, PyTorch, Data Lake, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Kubernetes, AKS, CI/CD, Terraform, Git, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53fb69889e7f589a</t>
+          <t>https://www.indeed.com/viewjob?jk=3df1cead72a76b88</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior Engineer, MDR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>Tokio Marine HCC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R, Java</t>
+          <t>Cortex, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edefefd43be9dc66</t>
+          <t>https://www.indeed.com/viewjob?jk=4b46394a094462f4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>AI / Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Compass Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R, Java</t>
+          <t>Machine Learning Engineer, TensorFlow, PyTorch, OpenCV, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,427 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbf25f49dcaa3bab</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Compass</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Madison, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=be3d62c77468bade</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Compass Group</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f225032bbf5d84c7</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Compass</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Aventura, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1b07860a5889799</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Agentic Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>arrivia</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Scottsdale, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, Docker, CI/CD, Git, Kafka, Python, R</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=88140868e5fe967c</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Modus Closing</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Boston, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f3134c6730945c7c</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Sr Engineer - Stores &amp; Supply Chain</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Brooklyn Park, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Docker, CI/CD, Kafka, MongoDB, Cassandra, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=00968f936d1004ed</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Sr. Data Modeler 4D</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Genpact</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Databricks, PySpark, Hadoop, R, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=58941ecd857176c7</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Quantum Software Engineer - Nuclear</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Infleqtion</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, FastAPI, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Julia</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bfcb1894126dab65</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Fleet Enablement &amp; Insights</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>TORC Robotics</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, S3, Git, Databricks, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=37856ba8342c5bdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>AI Agent Developer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Delta Faucet Company</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Copilot, MLflow, Databricks, Power BI, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=379366fceb0a12ba</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>AI Solutions Engineer - Columbus, Ohio - NOT ACCEPTING AGENCY CANDIDATES</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Wasserstrom</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0b5bd1d4503d38</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Senior Platform Operations Engineer, Infrastucture</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Viome Life Sciences</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, AKS, Terraform, PostgreSQL, MySQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b687743491edb71c</t>
+          <t>https://www.indeed.com/viewjob?jk=837380d1395fd31b</t>
         </is>
       </c>
     </row>
